--- a/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel1cn.xlsx
+++ b/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel1cn.xlsx
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="40">
   <si>
     <t>日期</t>
     <phoneticPr fontId="6" type="noConversion"/>
@@ -115,7 +115,23 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>深创100ETF</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>PE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>买卖金额</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>日期</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>单位：元</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -129,10 +145,6 @@
   <si>
     <t>CCI</t>
     <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>深创100ETF</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>买卖金额</t>
@@ -159,8 +171,8 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>日期</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <t>买卖金额</t>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>最高价</t>
@@ -2345,7 +2357,7 @@
               <c:f>模型一!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -2507,6 +2519,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2516,7 +2531,7 @@
               <c:f>模型一!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -2678,6 +2693,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>108000</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>110000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2720,7 +2738,7 @@
               <c:f>模型一!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -2882,6 +2900,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2891,7 +2912,7 @@
               <c:f>模型一!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -3053,6 +3074,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>145128.58746697762</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>150477.71562624906</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3095,7 +3119,7 @@
               <c:f>模型一!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -3257,6 +3281,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3266,7 +3293,7 @@
               <c:f>模型一!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3428,6 +3455,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>37128.587466977624</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>40477.715626249061</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3449,11 +3479,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="160755712"/>
-        <c:axId val="160757248"/>
+        <c:axId val="528185984"/>
+        <c:axId val="528196736"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="160755712"/>
+        <c:axId val="528185984"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3496,14 +3526,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="160757248"/>
+        <c:crossAx val="528196736"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="160757248"/>
+        <c:axId val="528196736"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3554,7 +3584,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="160755712"/>
+        <c:crossAx val="528185984"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3726,7 +3756,7 @@
               <c:f>模型一计算CCI!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -3888,6 +3918,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3897,7 +3930,7 @@
               <c:f>模型一计算CCI!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4058,6 +4091,9 @@
                   <c:v>24000</c:v>
                 </c:pt>
                 <c:pt idx="53">
+                  <c:v>24000</c:v>
+                </c:pt>
+                <c:pt idx="54">
                   <c:v>24000</c:v>
                 </c:pt>
               </c:numCache>
@@ -4101,7 +4137,7 @@
               <c:f>模型一计算CCI!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4263,6 +4299,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4272,7 +4311,7 @@
               <c:f>模型一计算CCI!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4434,6 +4473,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>34096.741890604411</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>34883.591403841878</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4476,7 +4518,7 @@
               <c:f>模型一计算CCI!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4638,6 +4680,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4647,7 +4692,7 @@
               <c:f>模型一计算CCI!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4809,6 +4854,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>10096.741890604411</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>10883.591403841878</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4830,11 +4878,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="342870656"/>
-        <c:axId val="342872448"/>
+        <c:axId val="547031296"/>
+        <c:axId val="547033088"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="342870656"/>
+        <c:axId val="547031296"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4877,14 +4925,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="342872448"/>
+        <c:crossAx val="547033088"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="342872448"/>
+        <c:axId val="547033088"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4935,7 +4983,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="342870656"/>
+        <c:crossAx val="547031296"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5107,7 +5155,7 @@
               <c:f>模型一计算RSI!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -5269,6 +5317,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5278,7 +5329,7 @@
               <c:f>模型一计算RSI!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -5440,6 +5491,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>117000</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>119000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5482,7 +5536,7 @@
               <c:f>模型一计算RSI!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -5644,6 +5698,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5653,7 +5710,7 @@
               <c:f>模型一计算RSI!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -5815,6 +5872,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>156673.21389222765</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>162288.75705714276</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5857,7 +5917,7 @@
               <c:f>模型一计算RSI!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -6019,6 +6079,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6028,7 +6091,7 @@
               <c:f>模型一计算RSI!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6190,6 +6253,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>39673.21389222765</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>43288.757057142764</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6211,11 +6277,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="433785472"/>
-        <c:axId val="433840896"/>
+        <c:axId val="547074816"/>
+        <c:axId val="547076352"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="433785472"/>
+        <c:axId val="547074816"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6258,14 +6324,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="433840896"/>
+        <c:crossAx val="547076352"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="433840896"/>
+        <c:axId val="547076352"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6316,7 +6382,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="433785472"/>
+        <c:crossAx val="547074816"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -6488,7 +6554,7 @@
               <c:f>模型一计算KDJ!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -6650,6 +6716,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6659,7 +6728,7 @@
               <c:f>模型一计算KDJ!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -6821,6 +6890,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>110000</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>112000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6863,7 +6935,7 @@
               <c:f>模型一计算KDJ!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -7025,6 +7097,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7034,7 +7109,7 @@
               <c:f>模型一计算KDJ!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -7196,6 +7271,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>148295.55114779418</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>153717.76323510444</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7238,7 +7316,7 @@
               <c:f>模型一计算KDJ!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -7400,6 +7478,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7409,7 +7490,7 @@
               <c:f>模型一计算KDJ!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7571,6 +7652,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>38295.551147794176</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>41717.763235104445</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7592,11 +7676,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="434154880"/>
-        <c:axId val="467999360"/>
+        <c:axId val="548234368"/>
+        <c:axId val="548235904"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="434154880"/>
+        <c:axId val="548234368"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7639,14 +7723,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="467999360"/>
+        <c:crossAx val="548235904"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="467999360"/>
+        <c:axId val="548235904"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7697,7 +7781,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="434154880"/>
+        <c:crossAx val="548234368"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7869,7 +7953,7 @@
               <c:f>'模型一&amp;PE'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -8031,6 +8115,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8040,7 +8127,7 @@
               <c:f>'模型一&amp;PE'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -8202,6 +8289,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>108000</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>110000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8244,7 +8334,7 @@
               <c:f>'模型一&amp;PE'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -8406,6 +8496,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8415,7 +8508,7 @@
               <c:f>'模型一&amp;PE'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -8577,6 +8670,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>145128.58746697762</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>150477.71562624906</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8619,7 +8715,7 @@
               <c:f>'模型一&amp;PE'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -8781,6 +8877,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8790,7 +8889,7 @@
               <c:f>'模型一&amp;PE'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -8952,6 +9051,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>37128.587466977624</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>40477.715626249061</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8973,11 +9075,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="574255104"/>
-        <c:axId val="574256640"/>
+        <c:axId val="592802176"/>
+        <c:axId val="595994880"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="574255104"/>
+        <c:axId val="592802176"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9020,14 +9122,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="574256640"/>
+        <c:crossAx val="595994880"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="574256640"/>
+        <c:axId val="595994880"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9078,7 +9180,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="574255104"/>
+        <c:crossAx val="592802176"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -9632,7 +9734,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AC56"/>
+  <dimension ref="A1:AC57"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -11521,6 +11623,35 @@
         <v>37128.587466977624</v>
       </c>
     </row>
+    <row r="57" spans="1:9" ht="12.75">
+      <c r="A57" s="15">
+        <v>46022</v>
+      </c>
+      <c r="B57" s="16">
+        <v>1.0640000104904175</v>
+      </c>
+      <c r="C57" s="17">
+        <v>2000</v>
+      </c>
+      <c r="D57" s="18">
+        <v>1879.6992295875662</v>
+      </c>
+      <c r="E57" s="18">
+        <v>141426.4230663786</v>
+      </c>
+      <c r="F57" s="18">
+        <v>150477.71562624906</v>
+      </c>
+      <c r="G57" s="18">
+        <v>110000</v>
+      </c>
+      <c r="H57" s="18">
+        <v>150477.71562624906</v>
+      </c>
+      <c r="I57" s="18">
+        <v>40477.715626249061</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11532,7 +11663,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet6"/>
-  <dimension ref="A1:AC56"/>
+  <dimension ref="A1:AC57"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -11565,10 +11696,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="22" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C1" s="14" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D1" s="14" t="s">
         <v>3</v>
@@ -11589,7 +11720,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="13" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K1" s="12"/>
     </row>
@@ -13567,6 +13698,38 @@
       </c>
       <c r="J56" s="6">
         <v>-25.623704638394841</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" ht="12.75">
+      <c r="A57" s="15">
+        <v>46022</v>
+      </c>
+      <c r="B57" s="16">
+        <v>1.0640000104904175</v>
+      </c>
+      <c r="C57" s="17">
+        <v>0</v>
+      </c>
+      <c r="D57" s="18">
+        <v>0</v>
+      </c>
+      <c r="E57" s="18">
+        <v>32785.329943524514</v>
+      </c>
+      <c r="F57" s="18">
+        <v>34883.591403841878</v>
+      </c>
+      <c r="G57" s="18">
+        <v>24000</v>
+      </c>
+      <c r="H57" s="18">
+        <v>34883.591403841878</v>
+      </c>
+      <c r="I57" s="18">
+        <v>10883.591403841878</v>
+      </c>
+      <c r="J57" s="6">
+        <v>38.003913332402767</v>
       </c>
     </row>
   </sheetData>
@@ -13580,7 +13743,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet5"/>
-  <dimension ref="A1:AH56"/>
+  <dimension ref="A1:AH57"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -13614,10 +13777,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="22" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C1" s="14" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D1" s="14" t="s">
         <v>3</v>
@@ -13638,19 +13801,19 @@
         <v>8</v>
       </c>
       <c r="J1" s="13" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="K1" s="22" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="L1" s="19" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="M1" s="24" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="N1" s="11" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:34" ht="14.1" customHeight="1">
@@ -16261,6 +16424,50 @@
       </c>
       <c r="N56" s="1">
         <v>75.343075358499476</v>
+      </c>
+    </row>
+    <row r="57" spans="1:14" ht="12.75">
+      <c r="A57" s="15">
+        <v>46022</v>
+      </c>
+      <c r="B57" s="16">
+        <v>1.0640000104904175</v>
+      </c>
+      <c r="C57" s="17">
+        <v>2000</v>
+      </c>
+      <c r="D57" s="18">
+        <v>1879.6992295875662</v>
+      </c>
+      <c r="E57" s="18">
+        <v>152527.02580551748</v>
+      </c>
+      <c r="F57" s="18">
+        <v>162288.75705714276</v>
+      </c>
+      <c r="G57" s="18">
+        <v>119000</v>
+      </c>
+      <c r="H57" s="18">
+        <v>162288.75705714276</v>
+      </c>
+      <c r="I57" s="18">
+        <v>43288.757057142764</v>
+      </c>
+      <c r="J57" s="6">
+        <v>2.4000048637390137E-2</v>
+      </c>
+      <c r="K57" s="6">
+        <v>3.2977829855092559E-2</v>
+      </c>
+      <c r="L57" s="6">
+        <v>2.4000048637390137E-2</v>
+      </c>
+      <c r="M57" s="6">
+        <v>4.2461169415320556E-2</v>
+      </c>
+      <c r="N57" s="1">
+        <v>77.665854024250493</v>
       </c>
     </row>
   </sheetData>
@@ -16274,7 +16481,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:AH56"/>
+  <dimension ref="A1:AH57"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -16305,13 +16512,13 @@
   <sheetData>
     <row r="1" spans="1:34" s="11" customFormat="1" ht="27" customHeight="1">
       <c r="A1" s="13" t="s">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="B1" s="22" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C1" s="14" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="D1" s="14" t="s">
         <v>3</v>
@@ -16332,28 +16539,28 @@
         <v>8</v>
       </c>
       <c r="J1" s="13" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K1" s="13" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="L1" s="19" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="M1" s="19" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="N1" s="19" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="O1" s="19" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="P1" s="19" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="Q1" s="19" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:34" ht="14.1" customHeight="1">
@@ -19464,6 +19671,59 @@
       </c>
       <c r="Q56" s="1">
         <v>83.790672900129579</v>
+      </c>
+    </row>
+    <row r="57" spans="1:17" ht="12.75">
+      <c r="A57" s="15">
+        <v>46022</v>
+      </c>
+      <c r="B57" s="16">
+        <v>1.0640000104904175</v>
+      </c>
+      <c r="C57" s="17">
+        <v>2000</v>
+      </c>
+      <c r="D57" s="18">
+        <v>1879.6992295875662</v>
+      </c>
+      <c r="E57" s="18">
+        <v>144471.58056347485</v>
+      </c>
+      <c r="F57" s="18">
+        <v>153717.76323510444</v>
+      </c>
+      <c r="G57" s="18">
+        <v>112000</v>
+      </c>
+      <c r="H57" s="18">
+        <v>153717.76323510444</v>
+      </c>
+      <c r="I57" s="18">
+        <v>41717.763235104445</v>
+      </c>
+      <c r="J57" s="6">
+        <v>1.1139999628067017</v>
+      </c>
+      <c r="K57" s="6">
+        <v>1.0360000133514404</v>
+      </c>
+      <c r="L57" s="6">
+        <v>1.1510000228881836</v>
+      </c>
+      <c r="M57" s="6">
+        <v>0.6589999794960022</v>
+      </c>
+      <c r="N57" s="6">
+        <v>82.317072210415034</v>
+      </c>
+      <c r="O57" s="6">
+        <v>82.130142596708495</v>
+      </c>
+      <c r="P57" s="6">
+        <v>81.483167688714857</v>
+      </c>
+      <c r="Q57" s="1">
+        <v>83.424092412695785</v>
       </c>
     </row>
   </sheetData>
@@ -19477,7 +19737,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="A1:AC56"/>
+  <dimension ref="A1:AC57"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -19510,13 +19770,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="22" t="s">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="E1" s="14" t="s">
         <v>3</v>
@@ -19546,7 +19806,7 @@
         <v>2000</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="F2" s="4"/>
       <c r="G2" s="4"/>
@@ -19588,7 +19848,7 @@
       </c>
       <c r="K3" s="6"/>
       <c r="M3" s="21" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="N3" s="10" t="s">
         <v>10</v>
@@ -21529,6 +21789,38 @@
       </c>
       <c r="J56" s="18">
         <v>37128.587466977624</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" ht="12.75">
+      <c r="A57" s="15">
+        <v>46022</v>
+      </c>
+      <c r="B57" s="16">
+        <v>1.0640000104904175</v>
+      </c>
+      <c r="C57" s="16">
+        <v>31.129999160000001</v>
+      </c>
+      <c r="D57" s="17">
+        <v>2000</v>
+      </c>
+      <c r="E57" s="18">
+        <v>1879.6992295875662</v>
+      </c>
+      <c r="F57" s="18">
+        <v>141426.4230663786</v>
+      </c>
+      <c r="G57" s="18">
+        <v>150477.71562624906</v>
+      </c>
+      <c r="H57" s="18">
+        <v>110000</v>
+      </c>
+      <c r="I57" s="18">
+        <v>150477.71562624906</v>
+      </c>
+      <c r="J57" s="18">
+        <v>40477.715626249061</v>
       </c>
     </row>
   </sheetData>

--- a/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel1cn.xlsx
+++ b/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel1cn.xlsx
@@ -147,6 +147,10 @@
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
+    <t>深创100ETF</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>买卖金额</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -169,10 +173,6 @@
   <si>
     <t>RSI</t>
     <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>买卖金额</t>
-    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>最高价</t>
@@ -2357,7 +2357,7 @@
               <c:f>模型一!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -2522,6 +2522,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2531,7 +2534,7 @@
               <c:f>模型一!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -2696,6 +2699,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>110000</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>112000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2738,7 +2744,7 @@
               <c:f>模型一!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -2903,6 +2909,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2912,7 +2921,7 @@
               <c:f>模型一!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -3077,6 +3086,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>150477.71562624906</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>153609.12930365079</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3119,7 +3131,7 @@
               <c:f>模型一!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -3284,6 +3296,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3293,7 +3308,7 @@
               <c:f>模型一!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3458,6 +3473,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>40477.715626249061</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>41609.129303650785</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3479,11 +3497,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="528185984"/>
-        <c:axId val="528196736"/>
+        <c:axId val="379579008"/>
+        <c:axId val="380481920"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="528185984"/>
+        <c:axId val="379579008"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3526,14 +3544,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="528196736"/>
+        <c:crossAx val="380481920"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="528196736"/>
+        <c:axId val="380481920"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3584,7 +3602,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="528185984"/>
+        <c:crossAx val="379579008"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3756,7 +3774,7 @@
               <c:f>模型一计算CCI!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -3921,6 +3939,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3930,7 +3951,7 @@
               <c:f>模型一计算CCI!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4095,6 +4116,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>24000</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>26000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4137,7 +4161,7 @@
               <c:f>模型一计算CCI!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4302,6 +4326,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4311,7 +4338,7 @@
               <c:f>模型一计算CCI!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4476,6 +4503,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>34883.591403841878</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>37145.874574921043</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4518,7 +4548,7 @@
               <c:f>模型一计算CCI!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4683,6 +4713,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4692,7 +4725,7 @@
               <c:f>模型一计算CCI!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4857,6 +4890,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>10883.591403841878</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>11145.874574921043</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4878,11 +4914,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="547031296"/>
-        <c:axId val="547033088"/>
+        <c:axId val="380496128"/>
+        <c:axId val="380497920"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="547031296"/>
+        <c:axId val="380496128"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4925,14 +4961,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="547033088"/>
+        <c:crossAx val="380497920"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="547033088"/>
+        <c:axId val="380497920"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4983,7 +5019,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="547031296"/>
+        <c:crossAx val="380496128"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5155,7 +5191,7 @@
               <c:f>模型一计算RSI!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -5320,6 +5356,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5329,7 +5368,7 @@
               <c:f>模型一计算RSI!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -5494,6 +5533,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>119000</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>121000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5536,7 +5578,7 @@
               <c:f>模型一计算RSI!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -5701,6 +5743,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5710,7 +5755,7 @@
               <c:f>模型一计算RSI!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -5875,6 +5920,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>162288.75705714276</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>165508.97573642572</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5917,7 +5965,7 @@
               <c:f>模型一计算RSI!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -6082,6 +6130,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6091,7 +6142,7 @@
               <c:f>模型一计算RSI!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6256,6 +6307,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>43288.757057142764</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>44508.975736425724</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6277,11 +6331,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="547074816"/>
-        <c:axId val="547076352"/>
+        <c:axId val="506414592"/>
+        <c:axId val="506416512"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="547074816"/>
+        <c:axId val="506414592"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6324,14 +6378,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="547076352"/>
+        <c:crossAx val="506416512"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="547076352"/>
+        <c:axId val="506416512"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6382,7 +6436,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="547074816"/>
+        <c:crossAx val="506414592"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -6554,7 +6608,7 @@
               <c:f>模型一计算KDJ!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -6719,6 +6773,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6728,7 +6785,7 @@
               <c:f>模型一计算KDJ!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -6893,6 +6950,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>112000</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>114000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6935,7 +6995,7 @@
               <c:f>模型一计算KDJ!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -7100,6 +7160,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7109,7 +7172,7 @@
               <c:f>模型一计算KDJ!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -7274,6 +7337,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>153717.76323510444</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>156873.53822185245</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7316,7 +7382,7 @@
               <c:f>模型一计算KDJ!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -7481,6 +7547,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7490,7 +7559,7 @@
               <c:f>模型一计算KDJ!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7655,6 +7724,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>41717.763235104445</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>42873.538221852446</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7676,11 +7748,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="548234368"/>
-        <c:axId val="548235904"/>
+        <c:axId val="558538752"/>
+        <c:axId val="578781952"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="548234368"/>
+        <c:axId val="558538752"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7723,14 +7795,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="548235904"/>
+        <c:crossAx val="578781952"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="548235904"/>
+        <c:axId val="578781952"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7781,7 +7853,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="548234368"/>
+        <c:crossAx val="558538752"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7953,7 +8025,7 @@
               <c:f>'模型一&amp;PE'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -8118,6 +8190,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8127,7 +8202,7 @@
               <c:f>'模型一&amp;PE'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -8292,6 +8367,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>110000</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>112000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8334,7 +8412,7 @@
               <c:f>'模型一&amp;PE'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -8499,6 +8577,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8508,7 +8589,7 @@
               <c:f>'模型一&amp;PE'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -8673,6 +8754,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>150477.71562624906</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>153609.12930365079</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8715,7 +8799,7 @@
               <c:f>'模型一&amp;PE'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -8880,6 +8964,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8889,7 +8976,7 @@
               <c:f>'模型一&amp;PE'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9054,6 +9141,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>40477.715626249061</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>41609.129303650785</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9075,11 +9165,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="592802176"/>
-        <c:axId val="595994880"/>
+        <c:axId val="581216512"/>
+        <c:axId val="581226880"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="592802176"/>
+        <c:axId val="581216512"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9122,14 +9212,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="595994880"/>
+        <c:crossAx val="581226880"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="595994880"/>
+        <c:axId val="581226880"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9180,7 +9270,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="592802176"/>
+        <c:crossAx val="581216512"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -9734,7 +9824,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AC57"/>
+  <dimension ref="A1:AC58"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -11652,6 +11742,35 @@
         <v>40477.715626249061</v>
       </c>
     </row>
+    <row r="58" spans="1:9" ht="12.75">
+      <c r="A58" s="15">
+        <v>46052</v>
+      </c>
+      <c r="B58" s="16">
+        <v>1.0720000267028809</v>
+      </c>
+      <c r="C58" s="17">
+        <v>2000</v>
+      </c>
+      <c r="D58" s="18">
+        <v>1865.6715953182777</v>
+      </c>
+      <c r="E58" s="18">
+        <v>143292.09466169687</v>
+      </c>
+      <c r="F58" s="18">
+        <v>153609.12930365079</v>
+      </c>
+      <c r="G58" s="18">
+        <v>112000</v>
+      </c>
+      <c r="H58" s="18">
+        <v>153609.12930365079</v>
+      </c>
+      <c r="I58" s="18">
+        <v>41609.129303650785</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11663,7 +11782,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet6"/>
-  <dimension ref="A1:AC57"/>
+  <dimension ref="A1:AC58"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -11731,7 +11850,7 @@
         <v>2000</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="E2" s="4"/>
       <c r="F2" s="4"/>
@@ -13730,6 +13849,38 @@
       </c>
       <c r="J57" s="6">
         <v>38.003913332402767</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" ht="12.75">
+      <c r="A58" s="15">
+        <v>46052</v>
+      </c>
+      <c r="B58" s="16">
+        <v>1.0720000267028809</v>
+      </c>
+      <c r="C58" s="17">
+        <v>2000</v>
+      </c>
+      <c r="D58" s="18">
+        <v>1865.6715953182777</v>
+      </c>
+      <c r="E58" s="18">
+        <v>34651.001538842793</v>
+      </c>
+      <c r="F58" s="18">
+        <v>37145.874574921043</v>
+      </c>
+      <c r="G58" s="18">
+        <v>26000</v>
+      </c>
+      <c r="H58" s="18">
+        <v>37145.874574921043</v>
+      </c>
+      <c r="I58" s="18">
+        <v>11145.874574921043</v>
+      </c>
+      <c r="J58" s="6">
+        <v>-130.04693515337254</v>
       </c>
     </row>
   </sheetData>
@@ -13743,7 +13894,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet5"/>
-  <dimension ref="A1:AH57"/>
+  <dimension ref="A1:AH58"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -13777,10 +13928,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="22" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="C1" s="14" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D1" s="14" t="s">
         <v>3</v>
@@ -13801,19 +13952,19 @@
         <v>8</v>
       </c>
       <c r="J1" s="13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K1" s="22" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L1" s="19" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M1" s="24" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N1" s="11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:34" ht="14.1" customHeight="1">
@@ -13823,7 +13974,7 @@
         <v>2000</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="E2" s="4"/>
       <c r="F2" s="4"/>
@@ -16468,6 +16619,50 @@
       </c>
       <c r="N57" s="1">
         <v>77.665854024250493</v>
+      </c>
+    </row>
+    <row r="58" spans="1:14" ht="12.75">
+      <c r="A58" s="15">
+        <v>46052</v>
+      </c>
+      <c r="B58" s="16">
+        <v>1.0720000267028809</v>
+      </c>
+      <c r="C58" s="17">
+        <v>2000</v>
+      </c>
+      <c r="D58" s="18">
+        <v>1865.6715953182777</v>
+      </c>
+      <c r="E58" s="18">
+        <v>154392.69740083575</v>
+      </c>
+      <c r="F58" s="18">
+        <v>165508.97573642572</v>
+      </c>
+      <c r="G58" s="18">
+        <v>121000</v>
+      </c>
+      <c r="H58" s="18">
+        <v>165508.97573642572</v>
+      </c>
+      <c r="I58" s="18">
+        <v>44508.975736425724</v>
+      </c>
+      <c r="J58" s="6">
+        <v>8.0000162124633789E-3</v>
+      </c>
+      <c r="K58" s="6">
+        <v>2.8814860914654364E-2</v>
+      </c>
+      <c r="L58" s="6">
+        <v>8.0000162124633789E-3</v>
+      </c>
+      <c r="M58" s="6">
+        <v>3.6717643881511025E-2</v>
+      </c>
+      <c r="N58" s="1">
+        <v>78.476878875019352</v>
       </c>
     </row>
   </sheetData>
@@ -16481,7 +16676,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:AH57"/>
+  <dimension ref="A1:AH58"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -16518,7 +16713,7 @@
         <v>22</v>
       </c>
       <c r="C1" s="14" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="D1" s="14" t="s">
         <v>3</v>
@@ -16570,7 +16765,7 @@
         <v>2000</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="E2" s="4"/>
       <c r="F2" s="4"/>
@@ -19724,6 +19919,59 @@
       </c>
       <c r="Q57" s="1">
         <v>83.424092412695785</v>
+      </c>
+    </row>
+    <row r="58" spans="1:17" ht="12.75">
+      <c r="A58" s="15">
+        <v>46052</v>
+      </c>
+      <c r="B58" s="16">
+        <v>1.0720000267028809</v>
+      </c>
+      <c r="C58" s="17">
+        <v>2000</v>
+      </c>
+      <c r="D58" s="18">
+        <v>1865.6715953182777</v>
+      </c>
+      <c r="E58" s="18">
+        <v>146337.25215879313</v>
+      </c>
+      <c r="F58" s="18">
+        <v>156873.53822185245</v>
+      </c>
+      <c r="G58" s="18">
+        <v>114000</v>
+      </c>
+      <c r="H58" s="18">
+        <v>156873.53822185245</v>
+      </c>
+      <c r="I58" s="18">
+        <v>42873.538221852446</v>
+      </c>
+      <c r="J58" s="6">
+        <v>1.1050000190734863</v>
+      </c>
+      <c r="K58" s="6">
+        <v>1.0499999523162842</v>
+      </c>
+      <c r="L58" s="6">
+        <v>1.1510000228881836</v>
+      </c>
+      <c r="M58" s="6">
+        <v>0.7720000147819519</v>
+      </c>
+      <c r="N58" s="6">
+        <v>79.155674275563754</v>
+      </c>
+      <c r="O58" s="6">
+        <v>81.138653156326924</v>
+      </c>
+      <c r="P58" s="6">
+        <v>81.368329511252213</v>
+      </c>
+      <c r="Q58" s="1">
+        <v>80.679300446476333</v>
       </c>
     </row>
   </sheetData>
@@ -19737,7 +19985,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="A1:AC57"/>
+  <dimension ref="A1:AC58"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -21823,6 +22071,38 @@
         <v>40477.715626249061</v>
       </c>
     </row>
+    <row r="58" spans="1:10" ht="12.75">
+      <c r="A58" s="15">
+        <v>46052</v>
+      </c>
+      <c r="B58" s="16">
+        <v>1.0720000267028809</v>
+      </c>
+      <c r="C58" s="16">
+        <v>31.709999079999999</v>
+      </c>
+      <c r="D58" s="17">
+        <v>2000</v>
+      </c>
+      <c r="E58" s="18">
+        <v>1865.6715953182777</v>
+      </c>
+      <c r="F58" s="18">
+        <v>143292.09466169687</v>
+      </c>
+      <c r="G58" s="18">
+        <v>153609.12930365079</v>
+      </c>
+      <c r="H58" s="18">
+        <v>112000</v>
+      </c>
+      <c r="I58" s="18">
+        <v>153609.12930365079</v>
+      </c>
+      <c r="J58" s="18">
+        <v>41609.129303650785</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:J2"/>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel1cn.xlsx
+++ b/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel1cn.xlsx
@@ -115,24 +115,12 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>深创100ETF</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>PE</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>买卖金额</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>日期</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>单位：元</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>深创100ETF</t>
@@ -145,6 +133,10 @@
   <si>
     <t>CCI</t>
     <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>单位：元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>深创100ETF</t>
@@ -173,6 +165,14 @@
   <si>
     <t>RSI</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>深创100ETF</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>买卖金额</t>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>最高价</t>
@@ -2357,7 +2357,7 @@
               <c:f>模型一!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -2525,6 +2525,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2534,7 +2537,7 @@
               <c:f>模型一!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -2702,6 +2705,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>112000</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>114000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2744,7 +2750,7 @@
               <c:f>模型一!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -2912,6 +2918,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2921,7 +2930,7 @@
               <c:f>模型一!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -3089,6 +3098,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>153609.12930365079</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>156039.00859402367</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3131,7 +3143,7 @@
               <c:f>模型一!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -3299,6 +3311,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3308,7 +3323,7 @@
               <c:f>模型一!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3476,6 +3491,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>41609.129303650785</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>42039.008594023675</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3497,11 +3515,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="379579008"/>
-        <c:axId val="380481920"/>
+        <c:axId val="105673472"/>
+        <c:axId val="105675008"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="379579008"/>
+        <c:axId val="105673472"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3544,14 +3562,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="380481920"/>
+        <c:crossAx val="105675008"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="380481920"/>
+        <c:axId val="105675008"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3602,7 +3620,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="379579008"/>
+        <c:crossAx val="105673472"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3774,7 +3792,7 @@
               <c:f>模型一计算CCI!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -3942,6 +3960,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3951,7 +3972,7 @@
               <c:f>模型一计算CCI!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4118,6 +4139,9 @@
                   <c:v>24000</c:v>
                 </c:pt>
                 <c:pt idx="55">
+                  <c:v>26000</c:v>
+                </c:pt>
+                <c:pt idx="56">
                   <c:v>26000</c:v>
                 </c:pt>
               </c:numCache>
@@ -4161,7 +4185,7 @@
               <c:f>模型一计算CCI!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4329,6 +4353,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4338,7 +4365,7 @@
               <c:f>模型一计算CCI!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4506,6 +4533,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>37145.874574921043</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>37249.828306544514</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4548,7 +4578,7 @@
               <c:f>模型一计算CCI!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4716,6 +4746,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4725,7 +4758,7 @@
               <c:f>模型一计算CCI!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4893,6 +4926,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>11145.874574921043</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>11249.828306544514</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4914,11 +4950,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="380496128"/>
-        <c:axId val="380497920"/>
+        <c:axId val="392597888"/>
+        <c:axId val="392599808"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="380496128"/>
+        <c:axId val="392597888"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4961,14 +4997,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="380497920"/>
+        <c:crossAx val="392599808"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="380497920"/>
+        <c:axId val="392599808"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5019,7 +5055,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="380496128"/>
+        <c:crossAx val="392597888"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5191,7 +5227,7 @@
               <c:f>模型一计算RSI!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -5359,6 +5395,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5368,7 +5407,7 @@
               <c:f>模型一计算RSI!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -5536,6 +5575,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>121000</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>123000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5578,7 +5620,7 @@
               <c:f>模型一计算RSI!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -5746,6 +5788,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5755,7 +5800,7 @@
               <c:f>模型一计算RSI!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -5923,6 +5968,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>165508.97573642572</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>167972.15706791595</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5965,7 +6013,7 @@
               <c:f>模型一计算RSI!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -6133,6 +6181,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6142,7 +6193,7 @@
               <c:f>模型一计算RSI!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6310,6 +6361,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>44508.975736425724</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>44972.157067915949</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6331,11 +6385,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="506414592"/>
-        <c:axId val="506416512"/>
+        <c:axId val="392707072"/>
+        <c:axId val="392713344"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="506414592"/>
+        <c:axId val="392707072"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6378,14 +6432,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="506416512"/>
+        <c:crossAx val="392713344"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="506416512"/>
+        <c:axId val="392713344"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6436,7 +6490,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="506414592"/>
+        <c:crossAx val="392707072"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -6608,7 +6662,7 @@
               <c:f>模型一计算KDJ!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -6776,6 +6830,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6785,7 +6842,7 @@
               <c:f>模型一计算KDJ!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -6953,6 +7010,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>114000</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>116000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6995,7 +7055,7 @@
               <c:f>模型一计算KDJ!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -7163,6 +7223,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7172,7 +7235,7 @@
               <c:f>模型一计算KDJ!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -7340,6 +7403,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>156873.53822185245</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>159312.55304860655</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7382,7 +7448,7 @@
               <c:f>模型一计算KDJ!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -7550,6 +7616,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7559,7 +7628,7 @@
               <c:f>模型一计算KDJ!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7727,6 +7796,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>42873.538221852446</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>43312.553048606555</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7748,11 +7820,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="558538752"/>
-        <c:axId val="578781952"/>
+        <c:axId val="392752512"/>
+        <c:axId val="395580160"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="558538752"/>
+        <c:axId val="392752512"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7795,14 +7867,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="578781952"/>
+        <c:crossAx val="395580160"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="578781952"/>
+        <c:axId val="395580160"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7853,7 +7925,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="558538752"/>
+        <c:crossAx val="392752512"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -8025,7 +8097,7 @@
               <c:f>'模型一&amp;PE'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -8193,6 +8265,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8202,7 +8277,7 @@
               <c:f>'模型一&amp;PE'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -8370,6 +8445,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>112000</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>114000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8412,7 +8490,7 @@
               <c:f>'模型一&amp;PE'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -8580,6 +8658,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8589,7 +8670,7 @@
               <c:f>'模型一&amp;PE'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -8757,6 +8838,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>153609.12930365079</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>156039.00859402367</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8799,7 +8883,7 @@
               <c:f>'模型一&amp;PE'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -8967,6 +9051,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8976,7 +9063,7 @@
               <c:f>'模型一&amp;PE'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9144,6 +9231,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>41609.129303650785</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>42039.008594023675</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9165,11 +9255,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="581216512"/>
-        <c:axId val="581226880"/>
+        <c:axId val="508610432"/>
+        <c:axId val="614073088"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="581216512"/>
+        <c:axId val="508610432"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9212,14 +9302,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="581226880"/>
+        <c:crossAx val="614073088"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="581226880"/>
+        <c:axId val="614073088"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9270,7 +9360,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="581216512"/>
+        <c:crossAx val="508610432"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -9824,7 +9914,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AC58"/>
+  <dimension ref="A1:AC59"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -11771,6 +11861,35 @@
         <v>41609.129303650785</v>
       </c>
     </row>
+    <row r="59" spans="1:9" ht="12.75">
+      <c r="A59" s="15">
+        <v>46080</v>
+      </c>
+      <c r="B59" s="16">
+        <v>1.0750000476837158</v>
+      </c>
+      <c r="C59" s="17">
+        <v>2000</v>
+      </c>
+      <c r="D59" s="18">
+        <v>1860.4650337545247</v>
+      </c>
+      <c r="E59" s="18">
+        <v>145152.5596954514</v>
+      </c>
+      <c r="F59" s="18">
+        <v>156039.00859402367</v>
+      </c>
+      <c r="G59" s="18">
+        <v>114000</v>
+      </c>
+      <c r="H59" s="18">
+        <v>156039.00859402367</v>
+      </c>
+      <c r="I59" s="18">
+        <v>42039.008594023675</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11782,7 +11901,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet6"/>
-  <dimension ref="A1:AC58"/>
+  <dimension ref="A1:AC59"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -11812,13 +11931,13 @@
   <sheetData>
     <row r="1" spans="1:29" s="11" customFormat="1" ht="27" customHeight="1">
       <c r="A1" s="13" t="s">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="B1" s="22" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C1" s="14" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D1" s="14" t="s">
         <v>3</v>
@@ -11839,7 +11958,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="13" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="K1" s="12"/>
     </row>
@@ -11850,7 +11969,7 @@
         <v>2000</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E2" s="4"/>
       <c r="F2" s="4"/>
@@ -13881,6 +14000,38 @@
       </c>
       <c r="J58" s="6">
         <v>-130.04693515337254</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" ht="12.75">
+      <c r="A59" s="15">
+        <v>46080</v>
+      </c>
+      <c r="B59" s="16">
+        <v>1.0750000476837158</v>
+      </c>
+      <c r="C59" s="17">
+        <v>0</v>
+      </c>
+      <c r="D59" s="18">
+        <v>0</v>
+      </c>
+      <c r="E59" s="18">
+        <v>34651.001538842793</v>
+      </c>
+      <c r="F59" s="18">
+        <v>37249.828306544514</v>
+      </c>
+      <c r="G59" s="18">
+        <v>26000</v>
+      </c>
+      <c r="H59" s="18">
+        <v>37249.828306544514</v>
+      </c>
+      <c r="I59" s="18">
+        <v>11249.828306544514</v>
+      </c>
+      <c r="J59" s="6">
+        <v>38.965935849742465</v>
       </c>
     </row>
   </sheetData>
@@ -13894,7 +14045,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet5"/>
-  <dimension ref="A1:AH58"/>
+  <dimension ref="A1:AH59"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -13925,13 +14076,13 @@
   <sheetData>
     <row r="1" spans="1:34" s="11" customFormat="1" ht="27" customHeight="1">
       <c r="A1" s="13" t="s">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="B1" s="22" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C1" s="14" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D1" s="14" t="s">
         <v>3</v>
@@ -13952,19 +14103,19 @@
         <v>8</v>
       </c>
       <c r="J1" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="K1" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="L1" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="K1" s="22" t="s">
+      <c r="M1" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="L1" s="19" t="s">
+      <c r="N1" s="11" t="s">
         <v>29</v>
-      </c>
-      <c r="M1" s="24" t="s">
-        <v>30</v>
-      </c>
-      <c r="N1" s="11" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:34" ht="14.1" customHeight="1">
@@ -13974,7 +14125,7 @@
         <v>2000</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E2" s="4"/>
       <c r="F2" s="4"/>
@@ -16663,6 +16814,50 @@
       </c>
       <c r="N58" s="1">
         <v>78.476878875019352</v>
+      </c>
+    </row>
+    <row r="59" spans="1:14" ht="12.75">
+      <c r="A59" s="15">
+        <v>46080</v>
+      </c>
+      <c r="B59" s="16">
+        <v>1.0750000476837158</v>
+      </c>
+      <c r="C59" s="17">
+        <v>2000</v>
+      </c>
+      <c r="D59" s="18">
+        <v>1860.4650337545247</v>
+      </c>
+      <c r="E59" s="18">
+        <v>156253.16243459028</v>
+      </c>
+      <c r="F59" s="18">
+        <v>167972.15706791595</v>
+      </c>
+      <c r="G59" s="18">
+        <v>123000</v>
+      </c>
+      <c r="H59" s="18">
+        <v>167972.15706791595</v>
+      </c>
+      <c r="I59" s="18">
+        <v>44972.157067915949</v>
+      </c>
+      <c r="J59" s="6">
+        <v>3.0000209808349609E-3</v>
+      </c>
+      <c r="K59" s="6">
+        <v>2.4512387592351127E-2</v>
+      </c>
+      <c r="L59" s="6">
+        <v>3.0000209808349609E-3</v>
+      </c>
+      <c r="M59" s="6">
+        <v>3.1098040064731682E-2</v>
+      </c>
+      <c r="N59" s="1">
+        <v>78.82293398981966</v>
       </c>
     </row>
   </sheetData>
@@ -16676,7 +16871,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:AH58"/>
+  <dimension ref="A1:AH59"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -16710,10 +16905,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="22" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="C1" s="14" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="D1" s="14" t="s">
         <v>3</v>
@@ -16765,7 +16960,7 @@
         <v>2000</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E2" s="4"/>
       <c r="F2" s="4"/>
@@ -19972,6 +20167,59 @@
       </c>
       <c r="Q58" s="1">
         <v>80.679300446476333</v>
+      </c>
+    </row>
+    <row r="59" spans="1:17" ht="12.75">
+      <c r="A59" s="15">
+        <v>46080</v>
+      </c>
+      <c r="B59" s="16">
+        <v>1.0750000476837158</v>
+      </c>
+      <c r="C59" s="17">
+        <v>2000</v>
+      </c>
+      <c r="D59" s="18">
+        <v>1860.4650337545247</v>
+      </c>
+      <c r="E59" s="18">
+        <v>148197.71719254766</v>
+      </c>
+      <c r="F59" s="18">
+        <v>159312.55304860655</v>
+      </c>
+      <c r="G59" s="18">
+        <v>116000</v>
+      </c>
+      <c r="H59" s="18">
+        <v>159312.55304860655</v>
+      </c>
+      <c r="I59" s="18">
+        <v>43312.553048606555</v>
+      </c>
+      <c r="J59" s="6">
+        <v>1.0920000076293945</v>
+      </c>
+      <c r="K59" s="6">
+        <v>1.0470000505447388</v>
+      </c>
+      <c r="L59" s="6">
+        <v>1.1510000228881836</v>
+      </c>
+      <c r="M59" s="6">
+        <v>0.7720000147819519</v>
+      </c>
+      <c r="N59" s="6">
+        <v>79.947236522705992</v>
+      </c>
+      <c r="O59" s="6">
+        <v>80.74151427845328</v>
+      </c>
+      <c r="P59" s="6">
+        <v>81.15939110031924</v>
+      </c>
+      <c r="Q59" s="1">
+        <v>79.905760634721361</v>
       </c>
     </row>
   </sheetData>
@@ -19985,7 +20233,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="A1:AC58"/>
+  <dimension ref="A1:AC59"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -20018,13 +20266,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="C1" s="13" t="s">
-        <v>18</v>
-      </c>
       <c r="D1" s="14" t="s">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="E1" s="14" t="s">
         <v>3</v>
@@ -20054,7 +20302,7 @@
         <v>2000</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F2" s="4"/>
       <c r="G2" s="4"/>
@@ -20096,7 +20344,7 @@
       </c>
       <c r="K3" s="6"/>
       <c r="M3" s="21" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="N3" s="10" t="s">
         <v>10</v>
@@ -22101,6 +22349,38 @@
       </c>
       <c r="J58" s="18">
         <v>41609.129303650785</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" ht="12.75">
+      <c r="A59" s="15">
+        <v>46080</v>
+      </c>
+      <c r="B59" s="16">
+        <v>1.0750000476837158</v>
+      </c>
+      <c r="C59" s="16">
+        <v>31.549999239999998</v>
+      </c>
+      <c r="D59" s="17">
+        <v>2000</v>
+      </c>
+      <c r="E59" s="18">
+        <v>1860.4650337545247</v>
+      </c>
+      <c r="F59" s="18">
+        <v>145152.5596954514</v>
+      </c>
+      <c r="G59" s="18">
+        <v>156039.00859402367</v>
+      </c>
+      <c r="H59" s="18">
+        <v>114000</v>
+      </c>
+      <c r="I59" s="18">
+        <v>156039.00859402367</v>
+      </c>
+      <c r="J59" s="18">
+        <v>42039.008594023675</v>
       </c>
     </row>
   </sheetData>

--- a/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel1cn.xlsx
+++ b/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel1cn.xlsx
@@ -119,6 +119,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>单位：元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>日期</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
@@ -135,15 +139,11 @@
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
-    <t>单位：元</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <t>日期</t>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>深创100ETF</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>买卖金额</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -167,11 +167,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>深创100ETF</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <t>单位：元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>买卖金额</t>
+    <t>深创100ETF</t>
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
@@ -2357,7 +2357,7 @@
               <c:f>模型一!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -2528,6 +2528,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2537,7 +2540,7 @@
               <c:f>模型一!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -2708,6 +2711,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>114000</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>116000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2750,7 +2756,7 @@
               <c:f>模型一!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -2921,6 +2927,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2930,7 +2939,7 @@
               <c:f>模型一!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -3101,6 +3110,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>156039.00859402367</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>154119.87937698292</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3143,7 +3155,7 @@
               <c:f>模型一!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -3314,6 +3326,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3323,7 +3338,7 @@
               <c:f>模型一!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3494,6 +3509,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>42039.008594023675</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>38119.879376982921</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3515,11 +3533,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="105673472"/>
-        <c:axId val="105675008"/>
+        <c:axId val="376619776"/>
+        <c:axId val="376621696"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="105673472"/>
+        <c:axId val="376619776"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3562,14 +3580,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="105675008"/>
+        <c:crossAx val="376621696"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="105675008"/>
+        <c:axId val="376621696"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3620,7 +3638,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="105673472"/>
+        <c:crossAx val="376619776"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3792,7 +3810,7 @@
               <c:f>模型一计算CCI!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -3963,6 +3981,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3972,7 +3993,7 @@
               <c:f>模型一计算CCI!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4142,6 +4163,9 @@
                   <c:v>26000</c:v>
                 </c:pt>
                 <c:pt idx="56">
+                  <c:v>26000</c:v>
+                </c:pt>
+                <c:pt idx="57">
                   <c:v>26000</c:v>
                 </c:pt>
               </c:numCache>
@@ -4185,7 +4209,7 @@
               <c:f>模型一计算CCI!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4356,6 +4380,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4365,7 +4392,7 @@
               <c:f>模型一计算CCI!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4536,6 +4563,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>37249.828306544514</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>36314.248852654535</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4578,7 +4608,7 @@
               <c:f>模型一计算CCI!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4749,6 +4779,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4758,7 +4791,7 @@
               <c:f>模型一计算CCI!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4929,6 +4962,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>11249.828306544514</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>10314.248852654535</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4950,11 +4986,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="392597888"/>
-        <c:axId val="392599808"/>
+        <c:axId val="390256896"/>
+        <c:axId val="393920512"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="392597888"/>
+        <c:axId val="390256896"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4997,14 +5033,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="392599808"/>
+        <c:crossAx val="393920512"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="392599808"/>
+        <c:axId val="393920512"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5055,7 +5091,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="392597888"/>
+        <c:crossAx val="390256896"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5227,7 +5263,7 @@
               <c:f>模型一计算RSI!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -5398,6 +5434,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5407,7 +5446,7 @@
               <c:f>模型一计算RSI!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -5578,6 +5617,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>123000</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>125000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5620,7 +5662,7 @@
               <c:f>模型一计算RSI!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -5791,6 +5833,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5800,7 +5845,7 @@
               <c:f>模型一计算RSI!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -5971,6 +6016,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>167972.15706791595</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>165753.31080411418</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6013,7 +6061,7 @@
               <c:f>模型一计算RSI!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -6184,6 +6232,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6193,7 +6244,7 @@
               <c:f>模型一计算RSI!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6364,6 +6415,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>44972.157067915949</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>40753.310804114182</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6385,11 +6439,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="392707072"/>
-        <c:axId val="392713344"/>
+        <c:axId val="433066368"/>
+        <c:axId val="433068288"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="392707072"/>
+        <c:axId val="433066368"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6432,14 +6486,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="392713344"/>
+        <c:crossAx val="433068288"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="392713344"/>
+        <c:axId val="433068288"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6490,7 +6544,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="392707072"/>
+        <c:crossAx val="433066368"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -6662,7 +6716,7 @@
               <c:f>模型一计算KDJ!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -6833,6 +6887,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6842,7 +6899,7 @@
               <c:f>模型一计算KDJ!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -7013,6 +7070,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>116000</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>118000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7055,7 +7115,7 @@
               <c:f>模型一计算KDJ!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -7226,6 +7286,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7235,7 +7298,7 @@
               <c:f>模型一计算KDJ!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -7406,6 +7469,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>159312.55304860655</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>157311.20436714575</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7448,7 +7514,7 @@
               <c:f>模型一计算KDJ!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -7619,6 +7685,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7628,7 +7697,7 @@
               <c:f>模型一计算KDJ!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7799,6 +7868,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>43312.553048606555</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>39311.20436714575</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7820,11 +7892,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="392752512"/>
-        <c:axId val="395580160"/>
+        <c:axId val="440569216"/>
+        <c:axId val="440587392"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="392752512"/>
+        <c:axId val="440569216"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7867,14 +7939,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="395580160"/>
+        <c:crossAx val="440587392"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="395580160"/>
+        <c:axId val="440587392"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7925,7 +7997,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="392752512"/>
+        <c:crossAx val="440569216"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -8097,7 +8169,7 @@
               <c:f>'模型一&amp;PE'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -8268,6 +8340,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8277,7 +8352,7 @@
               <c:f>'模型一&amp;PE'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -8448,6 +8523,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>114000</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>116000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8490,7 +8568,7 @@
               <c:f>'模型一&amp;PE'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -8661,6 +8739,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8670,7 +8751,7 @@
               <c:f>'模型一&amp;PE'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -8841,6 +8922,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>156039.00859402367</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>154119.87937698292</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8883,7 +8967,7 @@
               <c:f>'模型一&amp;PE'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -9054,6 +9138,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9063,7 +9150,7 @@
               <c:f>'模型一&amp;PE'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9234,6 +9321,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>42039.008594023675</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>38119.879376982921</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9255,11 +9345,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="508610432"/>
-        <c:axId val="614073088"/>
+        <c:axId val="494205568"/>
+        <c:axId val="500366720"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="508610432"/>
+        <c:axId val="494205568"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9302,14 +9392,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="614073088"/>
+        <c:crossAx val="500366720"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="614073088"/>
+        <c:axId val="500366720"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9360,7 +9450,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="508610432"/>
+        <c:crossAx val="494205568"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -9914,7 +10004,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AC59"/>
+  <dimension ref="A1:AC60"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -11890,6 +11980,35 @@
         <v>42039.008594023675</v>
       </c>
     </row>
+    <row r="60" spans="1:9" ht="12.75">
+      <c r="A60" s="15">
+        <v>46112</v>
+      </c>
+      <c r="B60" s="16">
+        <v>1.0479999780654907</v>
+      </c>
+      <c r="C60" s="17">
+        <v>2000</v>
+      </c>
+      <c r="D60" s="18">
+        <v>1908.3969865073964</v>
+      </c>
+      <c r="E60" s="18">
+        <v>147060.95668195881</v>
+      </c>
+      <c r="F60" s="18">
+        <v>154119.87937698292</v>
+      </c>
+      <c r="G60" s="18">
+        <v>116000</v>
+      </c>
+      <c r="H60" s="18">
+        <v>154119.87937698292</v>
+      </c>
+      <c r="I60" s="18">
+        <v>38119.879376982921</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11901,7 +12020,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet6"/>
-  <dimension ref="A1:AC59"/>
+  <dimension ref="A1:AC60"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -11931,13 +12050,13 @@
   <sheetData>
     <row r="1" spans="1:29" s="11" customFormat="1" ht="27" customHeight="1">
       <c r="A1" s="13" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B1" s="22" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C1" s="14" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D1" s="14" t="s">
         <v>3</v>
@@ -11958,7 +12077,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K1" s="12"/>
     </row>
@@ -11969,7 +12088,7 @@
         <v>2000</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E2" s="4"/>
       <c r="F2" s="4"/>
@@ -14032,6 +14151,38 @@
       </c>
       <c r="J59" s="6">
         <v>38.965935849742465</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" ht="12.75">
+      <c r="A60" s="15">
+        <v>46112</v>
+      </c>
+      <c r="B60" s="16">
+        <v>1.0479999780654907</v>
+      </c>
+      <c r="C60" s="17">
+        <v>0</v>
+      </c>
+      <c r="D60" s="18">
+        <v>0</v>
+      </c>
+      <c r="E60" s="18">
+        <v>34651.001538842793</v>
+      </c>
+      <c r="F60" s="18">
+        <v>36314.248852654535</v>
+      </c>
+      <c r="G60" s="18">
+        <v>26000</v>
+      </c>
+      <c r="H60" s="18">
+        <v>36314.248852654535</v>
+      </c>
+      <c r="I60" s="18">
+        <v>10314.248852654535</v>
+      </c>
+      <c r="J60" s="6">
+        <v>-89.784897005371036</v>
       </c>
     </row>
   </sheetData>
@@ -14045,7 +14196,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet5"/>
-  <dimension ref="A1:AH59"/>
+  <dimension ref="A1:AH60"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -14076,13 +14227,13 @@
   <sheetData>
     <row r="1" spans="1:34" s="11" customFormat="1" ht="27" customHeight="1">
       <c r="A1" s="13" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B1" s="22" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C1" s="14" t="s">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="D1" s="14" t="s">
         <v>3</v>
@@ -14125,7 +14276,7 @@
         <v>2000</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="E2" s="4"/>
       <c r="F2" s="4"/>
@@ -16858,6 +17009,50 @@
       </c>
       <c r="N59" s="1">
         <v>78.82293398981966</v>
+      </c>
+    </row>
+    <row r="60" spans="1:14" ht="12.75">
+      <c r="A60" s="15">
+        <v>46112</v>
+      </c>
+      <c r="B60" s="16">
+        <v>1.0479999780654907</v>
+      </c>
+      <c r="C60" s="17">
+        <v>2000</v>
+      </c>
+      <c r="D60" s="18">
+        <v>1908.3969865073964</v>
+      </c>
+      <c r="E60" s="18">
+        <v>158161.55942109769</v>
+      </c>
+      <c r="F60" s="18">
+        <v>165753.31080411418</v>
+      </c>
+      <c r="G60" s="18">
+        <v>125000</v>
+      </c>
+      <c r="H60" s="18">
+        <v>165753.31080411418</v>
+      </c>
+      <c r="I60" s="18">
+        <v>40753.310804114182</v>
+      </c>
+      <c r="J60" s="6">
+        <v>0</v>
+      </c>
+      <c r="K60" s="6">
+        <v>2.0426989660292605E-2</v>
+      </c>
+      <c r="L60" s="6">
+        <v>2.7000069618225098E-2</v>
+      </c>
+      <c r="M60" s="6">
+        <v>3.0415044990313916E-2</v>
+      </c>
+      <c r="N60" s="1">
+        <v>67.160806984825626</v>
       </c>
     </row>
   </sheetData>
@@ -16871,7 +17066,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:AH59"/>
+  <dimension ref="A1:AH60"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -16905,10 +17100,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="22" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C1" s="14" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="D1" s="14" t="s">
         <v>3</v>
@@ -16960,7 +17155,7 @@
         <v>2000</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E2" s="4"/>
       <c r="F2" s="4"/>
@@ -20220,6 +20415,59 @@
       </c>
       <c r="Q59" s="1">
         <v>79.905760634721361</v>
+      </c>
+    </row>
+    <row r="60" spans="1:17" ht="12.75">
+      <c r="A60" s="15">
+        <v>46112</v>
+      </c>
+      <c r="B60" s="16">
+        <v>1.0479999780654907</v>
+      </c>
+      <c r="C60" s="17">
+        <v>2000</v>
+      </c>
+      <c r="D60" s="18">
+        <v>1908.3969865073964</v>
+      </c>
+      <c r="E60" s="18">
+        <v>150106.11417905506</v>
+      </c>
+      <c r="F60" s="18">
+        <v>157311.20436714575</v>
+      </c>
+      <c r="G60" s="18">
+        <v>118000</v>
+      </c>
+      <c r="H60" s="18">
+        <v>157311.20436714575</v>
+      </c>
+      <c r="I60" s="18">
+        <v>39311.20436714575</v>
+      </c>
+      <c r="J60" s="6">
+        <v>1.1019999980926514</v>
+      </c>
+      <c r="K60" s="6">
+        <v>1.031000018119812</v>
+      </c>
+      <c r="L60" s="6">
+        <v>1.1510000228881836</v>
+      </c>
+      <c r="M60" s="6">
+        <v>0.80000001192092896</v>
+      </c>
+      <c r="N60" s="6">
+        <v>70.655258802170835</v>
+      </c>
+      <c r="O60" s="6">
+        <v>77.37942911969246</v>
+      </c>
+      <c r="P60" s="6">
+        <v>79.899403773443638</v>
+      </c>
+      <c r="Q60" s="1">
+        <v>72.339479812190092</v>
       </c>
     </row>
   </sheetData>
@@ -20233,7 +20481,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="A1:AC59"/>
+  <dimension ref="A1:AC60"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -20302,7 +20550,7 @@
         <v>2000</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F2" s="4"/>
       <c r="G2" s="4"/>
@@ -22381,6 +22629,38 @@
       </c>
       <c r="J59" s="18">
         <v>42039.008594023675</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" ht="12.75">
+      <c r="A60" s="15">
+        <v>46112</v>
+      </c>
+      <c r="B60" s="16">
+        <v>1.0479999780654907</v>
+      </c>
+      <c r="C60" s="16">
+        <v>30.549999239999998</v>
+      </c>
+      <c r="D60" s="17">
+        <v>2000</v>
+      </c>
+      <c r="E60" s="18">
+        <v>1908.3969865073964</v>
+      </c>
+      <c r="F60" s="18">
+        <v>147060.95668195881</v>
+      </c>
+      <c r="G60" s="18">
+        <v>154119.87937698292</v>
+      </c>
+      <c r="H60" s="18">
+        <v>116000</v>
+      </c>
+      <c r="I60" s="18">
+        <v>154119.87937698292</v>
+      </c>
+      <c r="J60" s="18">
+        <v>38119.879376982921</v>
       </c>
     </row>
   </sheetData>

--- a/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel1cn.xlsx
+++ b/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel1cn.xlsx
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="39">
   <si>
     <t>日期</t>
     <phoneticPr fontId="6" type="noConversion"/>
@@ -115,16 +115,16 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>深创100ETF</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>PE</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>单位：元</t>
     <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>日期</t>
-    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>深创100ETF</t>
@@ -141,10 +141,6 @@
   <si>
     <t>日期</t>
     <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>深创100ETF</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>MAX</t>
@@ -167,11 +163,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>单位：元</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <t>深创100ETF</t>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
-    <t>深创100ETF</t>
+    <t>买卖金额</t>
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
@@ -2357,7 +2353,7 @@
               <c:f>模型一!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -2531,6 +2527,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2540,7 +2539,7 @@
               <c:f>模型一!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -2714,6 +2713,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>116000</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>118000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2756,7 +2758,7 @@
               <c:f>模型一!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -2930,6 +2932,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2939,7 +2944,7 @@
               <c:f>模型一!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -3113,6 +3118,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>154119.87937698292</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>175090.75274658189</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3155,7 +3163,7 @@
               <c:f>模型一!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -3329,6 +3337,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3338,7 +3349,7 @@
               <c:f>模型一!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3512,6 +3523,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>38119.879376982921</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>57090.752746581886</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3533,11 +3547,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="376619776"/>
-        <c:axId val="376621696"/>
+        <c:axId val="91645824"/>
+        <c:axId val="459555584"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="376619776"/>
+        <c:axId val="91645824"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3580,14 +3594,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="376621696"/>
+        <c:crossAx val="459555584"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="376621696"/>
+        <c:axId val="459555584"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3638,7 +3652,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="376619776"/>
+        <c:crossAx val="91645824"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3810,7 +3824,7 @@
               <c:f>模型一计算CCI!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -3984,6 +3998,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3993,7 +4010,7 @@
               <c:f>模型一计算CCI!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4166,6 +4183,9 @@
                   <c:v>26000</c:v>
                 </c:pt>
                 <c:pt idx="57">
+                  <c:v>26000</c:v>
+                </c:pt>
+                <c:pt idx="58">
                   <c:v>26000</c:v>
                 </c:pt>
               </c:numCache>
@@ -4209,7 +4229,7 @@
               <c:f>模型一计算CCI!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4383,6 +4403,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4392,7 +4415,7 @@
               <c:f>模型一计算CCI!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4566,6 +4589,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>36314.248852654535</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>40784.23039741494</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4608,7 +4634,7 @@
               <c:f>模型一计算CCI!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4782,6 +4808,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4791,7 +4820,7 @@
               <c:f>模型一计算CCI!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4965,6 +4994,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>10314.248852654535</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>14784.23039741494</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4986,11 +5018,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="390256896"/>
-        <c:axId val="393920512"/>
+        <c:axId val="482577408"/>
+        <c:axId val="482579584"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="390256896"/>
+        <c:axId val="482577408"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5033,14 +5065,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="393920512"/>
+        <c:crossAx val="482579584"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="393920512"/>
+        <c:axId val="482579584"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5091,7 +5123,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="390256896"/>
+        <c:crossAx val="482577408"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5263,7 +5295,7 @@
               <c:f>模型一计算RSI!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -5437,6 +5469,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5446,7 +5481,7 @@
               <c:f>模型一计算RSI!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -5620,6 +5655,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>125000</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>127000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5662,7 +5700,7 @@
               <c:f>模型一计算RSI!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -5836,6 +5874,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5845,7 +5886,7 @@
               <c:f>模型一计算RSI!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -6019,6 +6060,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>165753.31080411418</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>188156.1626786936</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6061,7 +6105,7 @@
               <c:f>模型一计算RSI!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -6235,6 +6279,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6244,7 +6291,7 @@
               <c:f>模型一计算RSI!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6418,6 +6465,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>40753.310804114182</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>61156.162678693596</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6439,11 +6489,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="433066368"/>
-        <c:axId val="433068288"/>
+        <c:axId val="496235648"/>
+        <c:axId val="509187584"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="433066368"/>
+        <c:axId val="496235648"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6486,14 +6536,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="433068288"/>
+        <c:crossAx val="509187584"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="433068288"/>
+        <c:axId val="509187584"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6544,7 +6594,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="433066368"/>
+        <c:crossAx val="496235648"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -6716,7 +6766,7 @@
               <c:f>模型一计算KDJ!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -6890,6 +6940,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6899,7 +6952,7 @@
               <c:f>模型一计算KDJ!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -7073,6 +7126,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>118000</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>120000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7115,7 +7171,7 @@
               <c:f>模型一计算KDJ!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -7289,6 +7345,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7298,7 +7357,7 @@
               <c:f>模型一计算KDJ!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -7472,6 +7531,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>157311.20436714575</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>178674.90326006041</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7514,7 +7576,7 @@
               <c:f>模型一计算KDJ!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -7688,6 +7750,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7697,7 +7762,7 @@
               <c:f>模型一计算KDJ!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7871,6 +7936,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>39311.20436714575</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>58674.903260060411</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7892,11 +7960,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="440569216"/>
-        <c:axId val="440587392"/>
+        <c:axId val="512215680"/>
+        <c:axId val="522195712"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="440569216"/>
+        <c:axId val="512215680"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7939,14 +8007,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="440587392"/>
+        <c:crossAx val="522195712"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="440587392"/>
+        <c:axId val="522195712"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7997,7 +8065,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="440569216"/>
+        <c:crossAx val="512215680"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -8169,7 +8237,7 @@
               <c:f>'模型一&amp;PE'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -8343,6 +8411,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8352,7 +8423,7 @@
               <c:f>'模型一&amp;PE'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -8526,6 +8597,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>116000</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>118000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8568,7 +8642,7 @@
               <c:f>'模型一&amp;PE'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -8742,6 +8816,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8751,7 +8828,7 @@
               <c:f>'模型一&amp;PE'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -8925,6 +9002,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>154119.87937698292</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>175090.75274658189</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8967,7 +9047,7 @@
               <c:f>'模型一&amp;PE'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -9141,6 +9221,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9150,7 +9233,7 @@
               <c:f>'模型一&amp;PE'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9324,6 +9407,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>38119.879376982921</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>57090.752746581886</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9345,11 +9431,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="494205568"/>
-        <c:axId val="500366720"/>
+        <c:axId val="527165696"/>
+        <c:axId val="527249408"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="494205568"/>
+        <c:axId val="527165696"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9392,14 +9478,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="500366720"/>
+        <c:crossAx val="527249408"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="500366720"/>
+        <c:axId val="527249408"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9450,7 +9536,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="494205568"/>
+        <c:crossAx val="527165696"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -10004,7 +10090,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AC60"/>
+  <dimension ref="A1:AC61"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -12009,6 +12095,35 @@
         <v>38119.879376982921</v>
       </c>
     </row>
+    <row r="61" spans="1:9" ht="12.75">
+      <c r="A61" s="15">
+        <v>46142</v>
+      </c>
+      <c r="B61" s="16">
+        <v>1.1770000457763672</v>
+      </c>
+      <c r="C61" s="17">
+        <v>2000</v>
+      </c>
+      <c r="D61" s="18">
+        <v>1699.2352780078011</v>
+      </c>
+      <c r="E61" s="18">
+        <v>148760.19195996661</v>
+      </c>
+      <c r="F61" s="18">
+        <v>175090.75274658189</v>
+      </c>
+      <c r="G61" s="18">
+        <v>118000</v>
+      </c>
+      <c r="H61" s="18">
+        <v>175090.75274658189</v>
+      </c>
+      <c r="I61" s="18">
+        <v>57090.752746581886</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -12020,7 +12135,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet6"/>
-  <dimension ref="A1:AC60"/>
+  <dimension ref="A1:AC61"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -12050,7 +12165,7 @@
   <sheetData>
     <row r="1" spans="1:29" s="11" customFormat="1" ht="27" customHeight="1">
       <c r="A1" s="13" t="s">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="B1" s="22" t="s">
         <v>20</v>
@@ -12088,7 +12203,7 @@
         <v>2000</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E2" s="4"/>
       <c r="F2" s="4"/>
@@ -14183,6 +14298,38 @@
       </c>
       <c r="J60" s="6">
         <v>-89.784897005371036</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" ht="12.75">
+      <c r="A61" s="15">
+        <v>46142</v>
+      </c>
+      <c r="B61" s="16">
+        <v>1.1770000457763672</v>
+      </c>
+      <c r="C61" s="17">
+        <v>0</v>
+      </c>
+      <c r="D61" s="18">
+        <v>0</v>
+      </c>
+      <c r="E61" s="18">
+        <v>34651.001538842793</v>
+      </c>
+      <c r="F61" s="18">
+        <v>40784.23039741494</v>
+      </c>
+      <c r="G61" s="18">
+        <v>26000</v>
+      </c>
+      <c r="H61" s="18">
+        <v>40784.23039741494</v>
+      </c>
+      <c r="I61" s="18">
+        <v>14784.23039741494</v>
+      </c>
+      <c r="J61" s="6">
+        <v>95.218135798121537</v>
       </c>
     </row>
   </sheetData>
@@ -14196,7 +14343,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet5"/>
-  <dimension ref="A1:AH60"/>
+  <dimension ref="A1:AH61"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -14230,7 +14377,7 @@
         <v>23</v>
       </c>
       <c r="B1" s="22" t="s">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="C1" s="14" t="s">
         <v>2</v>
@@ -14254,19 +14401,19 @@
         <v>8</v>
       </c>
       <c r="J1" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="K1" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="K1" s="22" t="s">
+      <c r="L1" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="L1" s="19" t="s">
+      <c r="M1" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="M1" s="24" t="s">
+      <c r="N1" s="11" t="s">
         <v>28</v>
-      </c>
-      <c r="N1" s="11" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:34" ht="14.1" customHeight="1">
@@ -14276,7 +14423,7 @@
         <v>2000</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="E2" s="4"/>
       <c r="F2" s="4"/>
@@ -17053,6 +17200,50 @@
       </c>
       <c r="N60" s="1">
         <v>67.160806984825626</v>
+      </c>
+    </row>
+    <row r="61" spans="1:14" ht="12.75">
+      <c r="A61" s="15">
+        <v>46142</v>
+      </c>
+      <c r="B61" s="16">
+        <v>1.1770000457763672</v>
+      </c>
+      <c r="C61" s="17">
+        <v>2000</v>
+      </c>
+      <c r="D61" s="18">
+        <v>1699.2352780078011</v>
+      </c>
+      <c r="E61" s="18">
+        <v>159860.79469910549</v>
+      </c>
+      <c r="F61" s="18">
+        <v>188156.1626786936</v>
+      </c>
+      <c r="G61" s="18">
+        <v>127000</v>
+      </c>
+      <c r="H61" s="18">
+        <v>188156.1626786936</v>
+      </c>
+      <c r="I61" s="18">
+        <v>61156.162678693596</v>
+      </c>
+      <c r="J61" s="6">
+        <v>0.12900006771087646</v>
+      </c>
+      <c r="K61" s="6">
+        <v>3.8522502668723251E-2</v>
+      </c>
+      <c r="L61" s="6">
+        <v>0.12900006771087646</v>
+      </c>
+      <c r="M61" s="6">
+        <v>4.6845882110407668E-2</v>
+      </c>
+      <c r="N61" s="1">
+        <v>82.232420296691927</v>
       </c>
     </row>
   </sheetData>
@@ -17066,7 +17257,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:AH60"/>
+  <dimension ref="A1:AH61"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -17100,10 +17291,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="22" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C1" s="14" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="D1" s="14" t="s">
         <v>3</v>
@@ -17124,28 +17315,28 @@
         <v>8</v>
       </c>
       <c r="J1" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="K1" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="K1" s="13" t="s">
+      <c r="L1" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="L1" s="19" t="s">
+      <c r="M1" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="M1" s="19" t="s">
+      <c r="N1" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="N1" s="19" t="s">
+      <c r="O1" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="O1" s="19" t="s">
+      <c r="P1" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="P1" s="19" t="s">
+      <c r="Q1" s="19" t="s">
         <v>38</v>
-      </c>
-      <c r="Q1" s="19" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:34" ht="14.1" customHeight="1">
@@ -17155,7 +17346,7 @@
         <v>2000</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E2" s="4"/>
       <c r="F2" s="4"/>
@@ -20468,6 +20659,59 @@
       </c>
       <c r="Q60" s="1">
         <v>72.339479812190092</v>
+      </c>
+    </row>
+    <row r="61" spans="1:17" ht="12.75">
+      <c r="A61" s="15">
+        <v>46142</v>
+      </c>
+      <c r="B61" s="16">
+        <v>1.1770000457763672</v>
+      </c>
+      <c r="C61" s="17">
+        <v>2000</v>
+      </c>
+      <c r="D61" s="18">
+        <v>1699.2352780078011</v>
+      </c>
+      <c r="E61" s="18">
+        <v>151805.34945706287</v>
+      </c>
+      <c r="F61" s="18">
+        <v>178674.90326006041</v>
+      </c>
+      <c r="G61" s="18">
+        <v>120000</v>
+      </c>
+      <c r="H61" s="18">
+        <v>178674.90326006041</v>
+      </c>
+      <c r="I61" s="18">
+        <v>58674.903260060411</v>
+      </c>
+      <c r="J61" s="6">
+        <v>1.1909999847412109</v>
+      </c>
+      <c r="K61" s="6">
+        <v>1.031000018119812</v>
+      </c>
+      <c r="L61" s="6">
+        <v>1.1909999847412109</v>
+      </c>
+      <c r="M61" s="6">
+        <v>0.8399999737739563</v>
+      </c>
+      <c r="N61" s="6">
+        <v>96.011413524955756</v>
+      </c>
+      <c r="O61" s="6">
+        <v>83.590090588113569</v>
+      </c>
+      <c r="P61" s="6">
+        <v>81.129632711666943</v>
+      </c>
+      <c r="Q61" s="1">
+        <v>88.511006341006805</v>
       </c>
     </row>
   </sheetData>
@@ -20481,7 +20725,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="A1:AC60"/>
+  <dimension ref="A1:AC61"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -20514,10 +20758,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="22" t="s">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D1" s="14" t="s">
         <v>2</v>
@@ -20550,7 +20794,7 @@
         <v>2000</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F2" s="4"/>
       <c r="G2" s="4"/>
@@ -22661,6 +22905,38 @@
       </c>
       <c r="J60" s="18">
         <v>38119.879376982921</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" ht="12.75">
+      <c r="A61" s="15">
+        <v>46142</v>
+      </c>
+      <c r="B61" s="16">
+        <v>1.1770000457763672</v>
+      </c>
+      <c r="C61" s="16">
+        <v>34.549999239999998</v>
+      </c>
+      <c r="D61" s="17">
+        <v>2000</v>
+      </c>
+      <c r="E61" s="18">
+        <v>1699.2352780078011</v>
+      </c>
+      <c r="F61" s="18">
+        <v>148760.19195996661</v>
+      </c>
+      <c r="G61" s="18">
+        <v>175090.75274658189</v>
+      </c>
+      <c r="H61" s="18">
+        <v>118000</v>
+      </c>
+      <c r="I61" s="18">
+        <v>175090.75274658189</v>
+      </c>
+      <c r="J61" s="18">
+        <v>57090.752746581886</v>
       </c>
     </row>
   </sheetData>

--- a/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel1cn.xlsx
+++ b/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel1cn.xlsx
@@ -115,6 +115,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>日期</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
     <t>深创100ETF</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -139,8 +143,8 @@
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
-    <t>日期</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <t>买卖金额</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>MAX</t>
@@ -161,10 +165,6 @@
   <si>
     <t>RSI</t>
     <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>深创100ETF</t>
-    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>买卖金额</t>
@@ -2353,7 +2353,7 @@
               <c:f>模型一!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -2530,6 +2530,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2539,7 +2542,7 @@
               <c:f>模型一!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -2716,6 +2719,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>118000</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>120000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2758,7 +2764,7 @@
               <c:f>模型一!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -2935,6 +2941,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2944,7 +2953,7 @@
               <c:f>模型一!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -3121,6 +3130,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>175090.75274658189</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>187206.43969950231</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3163,7 +3175,7 @@
               <c:f>模型一!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -3340,6 +3352,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3349,7 +3364,7 @@
               <c:f>模型一!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3526,6 +3541,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>57090.752746581886</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>67206.439699502313</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3547,11 +3565,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="91645824"/>
-        <c:axId val="459555584"/>
+        <c:axId val="438256384"/>
+        <c:axId val="438258304"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="91645824"/>
+        <c:axId val="438256384"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3594,14 +3612,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="459555584"/>
+        <c:crossAx val="438258304"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="459555584"/>
+        <c:axId val="438258304"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3652,7 +3670,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="91645824"/>
+        <c:crossAx val="438256384"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3824,7 +3842,7 @@
               <c:f>模型一计算CCI!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4001,6 +4019,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4010,7 +4031,7 @@
               <c:f>模型一计算CCI!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4186,6 +4207,9 @@
                   <c:v>26000</c:v>
                 </c:pt>
                 <c:pt idx="58">
+                  <c:v>26000</c:v>
+                </c:pt>
+                <c:pt idx="59">
                   <c:v>26000</c:v>
                 </c:pt>
               </c:numCache>
@@ -4229,7 +4253,7 @@
               <c:f>模型一计算CCI!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4406,6 +4430,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4415,7 +4442,7 @@
               <c:f>模型一计算CCI!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4592,6 +4619,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>40784.23039741494</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>43140.497081088128</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4634,7 +4664,7 @@
               <c:f>模型一计算CCI!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4811,6 +4841,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4820,7 +4853,7 @@
               <c:f>模型一计算CCI!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4997,6 +5030,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>14784.23039741494</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>17140.497081088128</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5018,11 +5054,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="482577408"/>
-        <c:axId val="482579584"/>
+        <c:axId val="438911744"/>
+        <c:axId val="438913664"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="482577408"/>
+        <c:axId val="438911744"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5065,14 +5101,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="482579584"/>
+        <c:crossAx val="438913664"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="482579584"/>
+        <c:axId val="438913664"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5123,7 +5159,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="482577408"/>
+        <c:crossAx val="438911744"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5295,7 +5331,7 @@
               <c:f>模型一计算RSI!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -5472,6 +5508,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5481,7 +5520,7 @@
               <c:f>模型一计算RSI!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -5658,6 +5697,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>127000</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>129000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5700,7 +5742,7 @@
               <c:f>模型一计算RSI!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -5877,6 +5919,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5886,7 +5931,7 @@
               <c:f>模型一计算RSI!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -6063,6 +6108,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>188156.1626786936</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>201026.69016266201</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6105,7 +6153,7 @@
               <c:f>模型一计算RSI!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -6282,6 +6330,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6291,7 +6342,7 @@
               <c:f>模型一计算RSI!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6468,6 +6519,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>61156.162678693596</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>72026.690162662009</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6489,11 +6543,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="496235648"/>
-        <c:axId val="509187584"/>
+        <c:axId val="497046272"/>
+        <c:axId val="497078272"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="496235648"/>
+        <c:axId val="497046272"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6536,14 +6590,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="509187584"/>
+        <c:crossAx val="497078272"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="509187584"/>
+        <c:axId val="497078272"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6594,7 +6648,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="496235648"/>
+        <c:crossAx val="497046272"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -6766,7 +6820,7 @@
               <c:f>模型一计算KDJ!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -6943,6 +6997,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6952,7 +7009,7 @@
               <c:f>模型一计算KDJ!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -7129,6 +7186,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>120000</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>122000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7171,7 +7231,7 @@
               <c:f>模型一计算KDJ!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -7348,6 +7408,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7357,7 +7420,7 @@
               <c:f>模型一计算KDJ!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -7534,6 +7597,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>178674.90326006041</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>190997.66079790759</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7576,7 +7642,7 @@
               <c:f>模型一计算KDJ!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -7753,6 +7819,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7762,7 +7831,7 @@
               <c:f>模型一计算KDJ!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7939,6 +8008,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>58674.903260060411</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>68997.660797907592</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7960,11 +8032,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="512215680"/>
-        <c:axId val="522195712"/>
+        <c:axId val="498555904"/>
+        <c:axId val="498557696"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="512215680"/>
+        <c:axId val="498555904"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8007,14 +8079,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="522195712"/>
+        <c:crossAx val="498557696"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="522195712"/>
+        <c:axId val="498557696"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8065,7 +8137,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="512215680"/>
+        <c:crossAx val="498555904"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -8237,7 +8309,7 @@
               <c:f>'模型一&amp;PE'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -8414,6 +8486,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8423,7 +8498,7 @@
               <c:f>'模型一&amp;PE'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -8600,6 +8675,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>118000</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>120000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8642,7 +8720,7 @@
               <c:f>'模型一&amp;PE'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -8819,6 +8897,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8828,7 +8909,7 @@
               <c:f>'模型一&amp;PE'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -9005,6 +9086,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>175090.75274658189</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>187206.43969950231</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9047,7 +9131,7 @@
               <c:f>'模型一&amp;PE'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -9224,6 +9308,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9233,7 +9320,7 @@
               <c:f>'模型一&amp;PE'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9410,6 +9497,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>57090.752746581886</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>67206.439699502313</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9431,11 +9521,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="527165696"/>
-        <c:axId val="527249408"/>
+        <c:axId val="624350336"/>
+        <c:axId val="624351872"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="527165696"/>
+        <c:axId val="624350336"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9478,14 +9568,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="527249408"/>
+        <c:crossAx val="624351872"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="527249408"/>
+        <c:axId val="624351872"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9536,7 +9626,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="527165696"/>
+        <c:crossAx val="624350336"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -10090,7 +10180,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AC61"/>
+  <dimension ref="A1:AC62"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -12124,6 +12214,35 @@
         <v>57090.752746581886</v>
       </c>
     </row>
+    <row r="62" spans="1:9" ht="12.75">
+      <c r="A62" s="15">
+        <v>46171</v>
+      </c>
+      <c r="B62" s="16">
+        <v>1.2450000047683716</v>
+      </c>
+      <c r="C62" s="17">
+        <v>2000</v>
+      </c>
+      <c r="D62" s="18">
+        <v>1606.4256966586067</v>
+      </c>
+      <c r="E62" s="18">
+        <v>150366.61765662523</v>
+      </c>
+      <c r="F62" s="18">
+        <v>187206.43969950231</v>
+      </c>
+      <c r="G62" s="18">
+        <v>120000</v>
+      </c>
+      <c r="H62" s="18">
+        <v>187206.43969950231</v>
+      </c>
+      <c r="I62" s="18">
+        <v>67206.439699502313</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -12135,7 +12254,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet6"/>
-  <dimension ref="A1:AC61"/>
+  <dimension ref="A1:AC62"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -12165,13 +12284,13 @@
   <sheetData>
     <row r="1" spans="1:29" s="11" customFormat="1" ht="27" customHeight="1">
       <c r="A1" s="13" t="s">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="B1" s="22" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C1" s="14" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D1" s="14" t="s">
         <v>3</v>
@@ -12192,7 +12311,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K1" s="12"/>
     </row>
@@ -12203,7 +12322,7 @@
         <v>2000</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E2" s="4"/>
       <c r="F2" s="4"/>
@@ -14330,6 +14449,38 @@
       </c>
       <c r="J61" s="6">
         <v>95.218135798121537</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" ht="12.75">
+      <c r="A62" s="15">
+        <v>46171</v>
+      </c>
+      <c r="B62" s="16">
+        <v>1.2450000047683716</v>
+      </c>
+      <c r="C62" s="17">
+        <v>0</v>
+      </c>
+      <c r="D62" s="18">
+        <v>0</v>
+      </c>
+      <c r="E62" s="18">
+        <v>34651.001538842793</v>
+      </c>
+      <c r="F62" s="18">
+        <v>43140.497081088128</v>
+      </c>
+      <c r="G62" s="18">
+        <v>26000</v>
+      </c>
+      <c r="H62" s="18">
+        <v>43140.497081088128</v>
+      </c>
+      <c r="I62" s="18">
+        <v>17140.497081088128</v>
+      </c>
+      <c r="J62" s="6">
+        <v>107.7933992308817</v>
       </c>
     </row>
   </sheetData>
@@ -14343,7 +14494,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet5"/>
-  <dimension ref="A1:AH61"/>
+  <dimension ref="A1:AH62"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -14374,13 +14525,13 @@
   <sheetData>
     <row r="1" spans="1:34" s="11" customFormat="1" ht="27" customHeight="1">
       <c r="A1" s="13" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B1" s="22" t="s">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="C1" s="14" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="D1" s="14" t="s">
         <v>3</v>
@@ -14401,19 +14552,19 @@
         <v>8</v>
       </c>
       <c r="J1" s="13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K1" s="22" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L1" s="19" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M1" s="24" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="N1" s="11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:34" ht="14.1" customHeight="1">
@@ -14423,7 +14574,7 @@
         <v>2000</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E2" s="4"/>
       <c r="F2" s="4"/>
@@ -17244,6 +17395,50 @@
       </c>
       <c r="N61" s="1">
         <v>82.232420296691927</v>
+      </c>
+    </row>
+    <row r="62" spans="1:14" ht="12.75">
+      <c r="A62" s="15">
+        <v>46171</v>
+      </c>
+      <c r="B62" s="16">
+        <v>1.2450000047683716</v>
+      </c>
+      <c r="C62" s="17">
+        <v>2000</v>
+      </c>
+      <c r="D62" s="18">
+        <v>1606.4256966586067</v>
+      </c>
+      <c r="E62" s="18">
+        <v>161467.2203957641</v>
+      </c>
+      <c r="F62" s="18">
+        <v>201026.69016266201</v>
+      </c>
+      <c r="G62" s="18">
+        <v>129000</v>
+      </c>
+      <c r="H62" s="18">
+        <v>201026.69016266201</v>
+      </c>
+      <c r="I62" s="18">
+        <v>72026.690162662009</v>
+      </c>
+      <c r="J62" s="6">
+        <v>6.7999958992004395E-2</v>
+      </c>
+      <c r="K62" s="6">
+        <v>4.3435412055936783E-2</v>
+      </c>
+      <c r="L62" s="6">
+        <v>6.7999958992004395E-2</v>
+      </c>
+      <c r="M62" s="6">
+        <v>5.037156159067379E-2</v>
+      </c>
+      <c r="N62" s="1">
+        <v>86.230028778736084</v>
       </c>
     </row>
   </sheetData>
@@ -17257,7 +17452,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:AH61"/>
+  <dimension ref="A1:AH62"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -17288,10 +17483,10 @@
   <sheetData>
     <row r="1" spans="1:34" s="11" customFormat="1" ht="27" customHeight="1">
       <c r="A1" s="13" t="s">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="B1" s="22" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="C1" s="14" t="s">
         <v>30</v>
@@ -17346,7 +17541,7 @@
         <v>2000</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E2" s="4"/>
       <c r="F2" s="4"/>
@@ -20712,6 +20907,59 @@
       </c>
       <c r="Q61" s="1">
         <v>88.511006341006805</v>
+      </c>
+    </row>
+    <row r="62" spans="1:17" ht="12.75">
+      <c r="A62" s="15">
+        <v>46171</v>
+      </c>
+      <c r="B62" s="16">
+        <v>1.2450000047683716</v>
+      </c>
+      <c r="C62" s="17">
+        <v>2000</v>
+      </c>
+      <c r="D62" s="18">
+        <v>1606.4256966586067</v>
+      </c>
+      <c r="E62" s="18">
+        <v>153411.77515372148</v>
+      </c>
+      <c r="F62" s="18">
+        <v>190997.66079790759</v>
+      </c>
+      <c r="G62" s="18">
+        <v>122000</v>
+      </c>
+      <c r="H62" s="18">
+        <v>190997.66079790759</v>
+      </c>
+      <c r="I62" s="18">
+        <v>68997.660797907592</v>
+      </c>
+      <c r="J62" s="6">
+        <v>1.2680000066757202</v>
+      </c>
+      <c r="K62" s="6">
+        <v>1.1660000085830688</v>
+      </c>
+      <c r="L62" s="6">
+        <v>1.2680000066757202</v>
+      </c>
+      <c r="M62" s="6">
+        <v>0.88899999856948853</v>
+      </c>
+      <c r="N62" s="6">
+        <v>93.931398043426469</v>
+      </c>
+      <c r="O62" s="6">
+        <v>87.037193073217864</v>
+      </c>
+      <c r="P62" s="6">
+        <v>83.098819498850574</v>
+      </c>
+      <c r="Q62" s="1">
+        <v>94.913940221952458</v>
       </c>
     </row>
   </sheetData>
@@ -20725,7 +20973,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="A1:AC61"/>
+  <dimension ref="A1:AC62"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -20755,13 +21003,13 @@
   <sheetData>
     <row r="1" spans="1:29" s="11" customFormat="1" ht="27" customHeight="1">
       <c r="A1" s="13" t="s">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="B1" s="22" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D1" s="14" t="s">
         <v>2</v>
@@ -20794,7 +21042,7 @@
         <v>2000</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F2" s="4"/>
       <c r="G2" s="4"/>
@@ -22937,6 +23185,38 @@
       </c>
       <c r="J61" s="18">
         <v>57090.752746581886</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" ht="12.75">
+      <c r="A62" s="15">
+        <v>46171</v>
+      </c>
+      <c r="B62" s="16">
+        <v>1.2450000047683716</v>
+      </c>
+      <c r="C62" s="16">
+        <v>35.509998320000001</v>
+      </c>
+      <c r="D62" s="17">
+        <v>2000</v>
+      </c>
+      <c r="E62" s="18">
+        <v>1606.4256966586067</v>
+      </c>
+      <c r="F62" s="18">
+        <v>150366.61765662523</v>
+      </c>
+      <c r="G62" s="18">
+        <v>187206.43969950231</v>
+      </c>
+      <c r="H62" s="18">
+        <v>120000</v>
+      </c>
+      <c r="I62" s="18">
+        <v>187206.43969950231</v>
+      </c>
+      <c r="J62" s="18">
+        <v>67206.439699502313</v>
       </c>
     </row>
   </sheetData>
